--- a/online_experiment/crowding_stationary_dynamic_flies_online.xlsx
+++ b/online_experiment/crowding_stationary_dynamic_flies_online.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/helenhu/Documents/GitHub/crowded-dynamic-fixation/online_experiment/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fh986/Documents/Github/crowded-dynamic-fixation/online_experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C169A92-D3CD-034B-86FD-23EEB8C565CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FDC58F4-F99E-AD47-A5FD-7C7AFBADCD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="760" windowWidth="29280" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10780" yWindow="2020" windowWidth="29280" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -635,6 +635,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="33.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -717,64 +720,28 @@
         <v>6</v>
       </c>
       <c r="O6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" t="b">
-        <v>1</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" t="b">
-        <v>1</v>
-      </c>
-      <c r="N7" t="b">
-        <v>1</v>
-      </c>
       <c r="O7" t="s">
         <v>10</v>
       </c>
@@ -799,40 +766,40 @@
         <v>13</v>
       </c>
       <c r="C8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
@@ -858,40 +825,40 @@
         <v>14</v>
       </c>
       <c r="C9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
@@ -916,41 +883,41 @@
       <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I10" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" t="s">
-        <v>73</v>
-      </c>
-      <c r="K10" t="s">
-        <v>74</v>
-      </c>
-      <c r="L10" t="s">
-        <v>75</v>
-      </c>
-      <c r="M10" t="s">
-        <v>76</v>
-      </c>
-      <c r="N10" t="s">
-        <v>77</v>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
@@ -975,41 +942,41 @@
       <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-      <c r="D11">
-        <v>10</v>
-      </c>
-      <c r="E11">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>10</v>
-      </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-      <c r="H11">
-        <v>10</v>
-      </c>
-      <c r="I11">
-        <v>10</v>
-      </c>
-      <c r="J11">
-        <v>10</v>
-      </c>
-      <c r="K11">
-        <v>10</v>
-      </c>
-      <c r="L11">
-        <v>10</v>
-      </c>
-      <c r="M11">
-        <v>10</v>
-      </c>
-      <c r="N11">
-        <v>10</v>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L11" t="s">
+        <v>75</v>
+      </c>
+      <c r="M11" t="s">
+        <v>76</v>
+      </c>
+      <c r="N11" t="s">
+        <v>77</v>
       </c>
       <c r="O11" t="s">
         <v>17</v>
@@ -1034,41 +1001,41 @@
       <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" t="s">
-        <v>25</v>
-      </c>
-      <c r="J12" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L12" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" t="s">
-        <v>25</v>
-      </c>
-      <c r="N12" t="s">
-        <v>25</v>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>10</v>
+      </c>
+      <c r="J12">
+        <v>10</v>
+      </c>
+      <c r="K12">
+        <v>10</v>
+      </c>
+      <c r="L12">
+        <v>10</v>
+      </c>
+      <c r="M12">
+        <v>10</v>
+      </c>
+      <c r="N12">
+        <v>10</v>
       </c>
       <c r="O12">
         <v>35</v>
@@ -1094,40 +1061,40 @@
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O13" t="s">
         <v>25</v>
@@ -1153,40 +1120,40 @@
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O14" t="s">
         <v>27</v>
@@ -1211,6 +1178,42 @@
       <c r="A15" t="s">
         <v>28</v>
       </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" t="s">
+        <v>29</v>
+      </c>
+      <c r="L15" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" t="s">
+        <v>29</v>
+      </c>
       <c r="O15" t="s">
         <v>29</v>
       </c>
@@ -1244,82 +1247,46 @@
       <c r="A18" t="s">
         <v>32</v>
       </c>
-      <c r="C18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J18" t="s">
-        <v>34</v>
-      </c>
-      <c r="K18" t="s">
-        <v>34</v>
-      </c>
-      <c r="L18" t="s">
-        <v>34</v>
-      </c>
-      <c r="M18" t="s">
-        <v>35</v>
-      </c>
-      <c r="N18" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>33</v>
       </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>-0.25</v>
-      </c>
-      <c r="H19">
-        <v>-0.25</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>-0.25</v>
-      </c>
-      <c r="N19">
-        <v>-0.25</v>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" t="s">
+        <v>34</v>
+      </c>
+      <c r="J19" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" t="s">
+        <v>34</v>
+      </c>
+      <c r="M19" t="s">
+        <v>35</v>
+      </c>
+      <c r="N19" t="s">
+        <v>35</v>
       </c>
       <c r="O19" t="s">
         <v>34</v>
@@ -1345,40 +1312,40 @@
         <v>36</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>-0.25</v>
       </c>
       <c r="H20">
-        <v>2</v>
+        <v>-0.25</v>
       </c>
       <c r="I20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>2</v>
+        <v>-0.25</v>
       </c>
       <c r="N20">
-        <v>2</v>
+        <v>-0.25</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -1403,41 +1370,41 @@
       <c r="A21" t="s">
         <v>37</v>
       </c>
-      <c r="C21" t="b">
-        <v>1</v>
-      </c>
-      <c r="D21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" t="b">
-        <v>1</v>
-      </c>
-      <c r="L21" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" t="b">
-        <v>1</v>
-      </c>
-      <c r="N21" t="b">
-        <v>1</v>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21">
+        <v>2</v>
+      </c>
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <v>2</v>
       </c>
       <c r="O21">
         <v>2</v>
@@ -1462,41 +1429,41 @@
       <c r="A22" t="s">
         <v>38</v>
       </c>
-      <c r="C22">
-        <v>0.15</v>
-      </c>
-      <c r="D22">
-        <v>0.15</v>
-      </c>
-      <c r="E22">
-        <v>0.15</v>
-      </c>
-      <c r="F22">
-        <v>0.15</v>
-      </c>
-      <c r="G22">
-        <v>0.15</v>
-      </c>
-      <c r="H22">
-        <v>0.15</v>
-      </c>
-      <c r="I22">
-        <v>0.15</v>
-      </c>
-      <c r="J22">
-        <v>0.15</v>
-      </c>
-      <c r="K22">
-        <v>0.15</v>
-      </c>
-      <c r="L22">
-        <v>0.15</v>
-      </c>
-      <c r="M22">
-        <v>0.15</v>
-      </c>
-      <c r="N22">
-        <v>0.15</v>
+      <c r="C22" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
       </c>
       <c r="O22" t="b">
         <v>1</v>
@@ -1521,41 +1488,41 @@
       <c r="A23" t="s">
         <v>39</v>
       </c>
-      <c r="C23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" t="s">
-        <v>41</v>
-      </c>
-      <c r="G23" t="s">
-        <v>41</v>
-      </c>
-      <c r="H23" t="s">
-        <v>41</v>
-      </c>
-      <c r="I23" t="s">
-        <v>41</v>
-      </c>
-      <c r="J23" t="s">
-        <v>41</v>
-      </c>
-      <c r="K23" t="s">
-        <v>41</v>
-      </c>
-      <c r="L23" t="s">
-        <v>41</v>
-      </c>
-      <c r="M23" t="s">
-        <v>41</v>
-      </c>
-      <c r="N23" t="s">
-        <v>41</v>
+      <c r="C23">
+        <v>0.15</v>
+      </c>
+      <c r="D23">
+        <v>0.15</v>
+      </c>
+      <c r="E23">
+        <v>0.15</v>
+      </c>
+      <c r="F23">
+        <v>0.15</v>
+      </c>
+      <c r="G23">
+        <v>0.15</v>
+      </c>
+      <c r="H23">
+        <v>0.15</v>
+      </c>
+      <c r="I23">
+        <v>0.15</v>
+      </c>
+      <c r="J23">
+        <v>0.15</v>
+      </c>
+      <c r="K23">
+        <v>0.15</v>
+      </c>
+      <c r="L23">
+        <v>0.15</v>
+      </c>
+      <c r="M23">
+        <v>0.15</v>
+      </c>
+      <c r="N23">
+        <v>0.15</v>
       </c>
       <c r="O23">
         <v>0.15</v>
@@ -1580,41 +1547,41 @@
       <c r="A24" t="s">
         <v>40</v>
       </c>
-      <c r="C24">
-        <v>0.5</v>
-      </c>
-      <c r="D24">
-        <v>0.5</v>
-      </c>
-      <c r="E24">
-        <v>0.5</v>
-      </c>
-      <c r="F24">
-        <v>0.5</v>
-      </c>
-      <c r="G24">
-        <v>0.5</v>
-      </c>
-      <c r="H24">
-        <v>0.5</v>
-      </c>
-      <c r="I24">
-        <v>0.5</v>
-      </c>
-      <c r="J24">
-        <v>0.5</v>
-      </c>
-      <c r="K24">
-        <v>0.5</v>
-      </c>
-      <c r="L24">
-        <v>0.5</v>
-      </c>
-      <c r="M24">
-        <v>0.5</v>
-      </c>
-      <c r="N24">
-        <v>0.5</v>
+      <c r="C24" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G24" t="s">
+        <v>41</v>
+      </c>
+      <c r="H24" t="s">
+        <v>41</v>
+      </c>
+      <c r="I24" t="s">
+        <v>41</v>
+      </c>
+      <c r="J24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K24" t="s">
+        <v>41</v>
+      </c>
+      <c r="L24" t="s">
+        <v>41</v>
+      </c>
+      <c r="M24" t="s">
+        <v>41</v>
+      </c>
+      <c r="N24" t="s">
+        <v>41</v>
       </c>
       <c r="O24" t="s">
         <v>41</v>
@@ -1640,40 +1607,40 @@
         <v>42</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E25">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F25">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G25">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H25">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K25">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="L25">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M25">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="N25">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O25">
         <v>0.5</v>
@@ -1699,40 +1666,40 @@
         <v>43</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="M26">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -1757,40 +1724,40 @@
       <c r="A27" t="s">
         <v>44</v>
       </c>
-      <c r="C27" t="b">
-        <v>1</v>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" t="b">
-        <v>1</v>
-      </c>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="b">
-        <v>1</v>
-      </c>
-      <c r="K27" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" t="b">
-        <v>1</v>
-      </c>
-      <c r="M27" t="b">
-        <v>1</v>
-      </c>
-      <c r="N27" t="b">
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
         <v>1</v>
       </c>
       <c r="O27">
@@ -1875,41 +1842,41 @@
       <c r="A29" t="s">
         <v>46</v>
       </c>
-      <c r="C29">
-        <v>1.25</v>
-      </c>
-      <c r="D29">
-        <v>1.25</v>
-      </c>
-      <c r="E29">
-        <v>1.25</v>
-      </c>
-      <c r="F29">
-        <v>1.25</v>
-      </c>
-      <c r="G29">
-        <v>1.25</v>
-      </c>
-      <c r="H29">
-        <v>1.25</v>
-      </c>
-      <c r="I29">
-        <v>1.25</v>
-      </c>
-      <c r="J29">
-        <v>1.25</v>
-      </c>
-      <c r="K29">
-        <v>1.25</v>
-      </c>
-      <c r="L29">
-        <v>1.25</v>
-      </c>
-      <c r="M29">
-        <v>1.25</v>
-      </c>
-      <c r="N29">
-        <v>1.25</v>
+      <c r="C29" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" t="b">
+        <v>1</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
       </c>
       <c r="O29" t="b">
         <v>1</v>
@@ -1935,40 +1902,40 @@
         <v>47</v>
       </c>
       <c r="C30">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="D30">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E30">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="F30">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="G30">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="H30">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="I30">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="J30">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="K30">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="L30">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="M30">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="N30">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="O30">
         <v>1.25</v>
@@ -1994,40 +1961,40 @@
         <v>48</v>
       </c>
       <c r="C31">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="D31">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="E31">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="F31">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="G31">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="H31">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="I31">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="J31">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="K31">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="L31">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="M31">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="N31">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="O31">
         <v>0.75</v>
@@ -2052,41 +2019,41 @@
       <c r="A32" t="s">
         <v>49</v>
       </c>
-      <c r="C32" t="b">
-        <v>1</v>
-      </c>
-      <c r="D32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" t="b">
-        <v>1</v>
-      </c>
-      <c r="I32" t="b">
-        <v>1</v>
-      </c>
-      <c r="J32" t="b">
-        <v>1</v>
-      </c>
-      <c r="K32" t="b">
-        <v>1</v>
-      </c>
-      <c r="L32" t="b">
-        <v>1</v>
-      </c>
-      <c r="M32" t="b">
-        <v>1</v>
-      </c>
-      <c r="N32" t="b">
-        <v>1</v>
+      <c r="C32">
+        <v>30</v>
+      </c>
+      <c r="D32">
+        <v>30</v>
+      </c>
+      <c r="E32">
+        <v>30</v>
+      </c>
+      <c r="F32">
+        <v>30</v>
+      </c>
+      <c r="G32">
+        <v>30</v>
+      </c>
+      <c r="H32">
+        <v>30</v>
+      </c>
+      <c r="I32">
+        <v>30</v>
+      </c>
+      <c r="J32">
+        <v>30</v>
+      </c>
+      <c r="K32">
+        <v>30</v>
+      </c>
+      <c r="L32">
+        <v>30</v>
+      </c>
+      <c r="M32">
+        <v>30</v>
+      </c>
+      <c r="N32">
+        <v>30</v>
       </c>
       <c r="O32">
         <v>30</v>
@@ -2112,40 +2079,40 @@
         <v>50</v>
       </c>
       <c r="C33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="b">
         <v>1</v>
@@ -2171,40 +2138,40 @@
         <v>51</v>
       </c>
       <c r="C34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="b">
         <v>0</v>
@@ -2229,41 +2196,41 @@
       <c r="A35" t="s">
         <v>52</v>
       </c>
-      <c r="C35">
-        <v>0.15</v>
-      </c>
-      <c r="D35">
-        <v>0.15</v>
-      </c>
-      <c r="E35">
-        <v>0.15</v>
-      </c>
-      <c r="F35">
-        <v>0.15</v>
-      </c>
-      <c r="G35">
-        <v>0.15</v>
-      </c>
-      <c r="H35">
-        <v>0.15</v>
-      </c>
-      <c r="I35">
-        <v>0.15</v>
-      </c>
-      <c r="J35">
-        <v>0.15</v>
-      </c>
-      <c r="K35">
-        <v>0.15</v>
-      </c>
-      <c r="L35">
-        <v>0.15</v>
-      </c>
-      <c r="M35">
-        <v>0.15</v>
-      </c>
-      <c r="N35">
-        <v>0.15</v>
+      <c r="C35" t="b">
+        <v>1</v>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
       </c>
       <c r="O35" t="b">
         <v>1</v>
@@ -2289,40 +2256,40 @@
         <v>53</v>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>0.15</v>
       </c>
       <c r="D36">
-        <v>-10</v>
+        <v>0.15</v>
       </c>
       <c r="E36">
-        <v>10</v>
+        <v>0.15</v>
       </c>
       <c r="F36">
-        <v>-10</v>
+        <v>0.15</v>
       </c>
       <c r="G36">
-        <v>10</v>
+        <v>0.15</v>
       </c>
       <c r="H36">
-        <v>-10</v>
+        <v>0.15</v>
       </c>
       <c r="I36">
-        <v>10</v>
+        <v>0.15</v>
       </c>
       <c r="J36">
-        <v>-10</v>
+        <v>0.15</v>
       </c>
       <c r="K36">
-        <v>10</v>
+        <v>0.15</v>
       </c>
       <c r="L36">
-        <v>-10</v>
+        <v>0.15</v>
       </c>
       <c r="M36">
-        <v>10</v>
+        <v>0.15</v>
       </c>
       <c r="N36">
-        <v>-10</v>
+        <v>0.15</v>
       </c>
       <c r="O36">
         <v>0.15</v>
@@ -2348,40 +2315,40 @@
         <v>54</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="O37">
         <v>10</v>
@@ -2406,41 +2373,41 @@
       <c r="A38" t="s">
         <v>55</v>
       </c>
-      <c r="C38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38" t="s">
-        <v>57</v>
-      </c>
-      <c r="E38" t="s">
-        <v>57</v>
-      </c>
-      <c r="F38" t="s">
-        <v>57</v>
-      </c>
-      <c r="G38" t="s">
-        <v>57</v>
-      </c>
-      <c r="H38" t="s">
-        <v>57</v>
-      </c>
-      <c r="I38" t="s">
-        <v>57</v>
-      </c>
-      <c r="J38" t="s">
-        <v>57</v>
-      </c>
-      <c r="K38" t="s">
-        <v>57</v>
-      </c>
-      <c r="L38" t="s">
-        <v>57</v>
-      </c>
-      <c r="M38" t="s">
-        <v>57</v>
-      </c>
-      <c r="N38" t="s">
-        <v>57</v>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -2466,40 +2433,40 @@
         <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O39" t="s">
         <v>57</v>
@@ -2524,41 +2491,41 @@
       <c r="A40" t="s">
         <v>58</v>
       </c>
-      <c r="C40">
-        <v>0.02</v>
-      </c>
-      <c r="D40">
-        <v>0.02</v>
-      </c>
-      <c r="E40">
-        <v>0.02</v>
-      </c>
-      <c r="F40">
-        <v>0.02</v>
-      </c>
-      <c r="G40">
-        <v>0.02</v>
-      </c>
-      <c r="H40">
-        <v>0.02</v>
-      </c>
-      <c r="I40">
-        <v>0.02</v>
-      </c>
-      <c r="J40">
-        <v>0.02</v>
-      </c>
-      <c r="K40">
-        <v>0.02</v>
-      </c>
-      <c r="L40">
-        <v>0.02</v>
-      </c>
-      <c r="M40">
-        <v>0.02</v>
-      </c>
-      <c r="N40">
-        <v>0.02</v>
+      <c r="C40" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" t="s">
+        <v>59</v>
+      </c>
+      <c r="F40" t="s">
+        <v>59</v>
+      </c>
+      <c r="G40" t="s">
+        <v>59</v>
+      </c>
+      <c r="H40" t="s">
+        <v>59</v>
+      </c>
+      <c r="I40" t="s">
+        <v>59</v>
+      </c>
+      <c r="J40" t="s">
+        <v>59</v>
+      </c>
+      <c r="K40" t="s">
+        <v>59</v>
+      </c>
+      <c r="L40" t="s">
+        <v>59</v>
+      </c>
+      <c r="M40" t="s">
+        <v>59</v>
+      </c>
+      <c r="N40" t="s">
+        <v>59</v>
       </c>
       <c r="O40" t="s">
         <v>59</v>
@@ -2584,40 +2551,40 @@
         <v>60</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="F41">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="G41">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="J41">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="K41">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="L41">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="M41">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="N41">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="O41">
         <v>0.02</v>
@@ -2642,41 +2609,41 @@
       <c r="A42" t="s">
         <v>61</v>
       </c>
-      <c r="C42" t="s">
-        <v>78</v>
-      </c>
-      <c r="D42" t="s">
-        <v>78</v>
-      </c>
-      <c r="E42" t="s">
-        <v>78</v>
-      </c>
-      <c r="F42" t="s">
-        <v>78</v>
-      </c>
-      <c r="G42" t="s">
-        <v>78</v>
-      </c>
-      <c r="H42" t="s">
-        <v>78</v>
-      </c>
-      <c r="I42" t="s">
-        <v>63</v>
-      </c>
-      <c r="J42" t="s">
-        <v>63</v>
-      </c>
-      <c r="K42" t="s">
-        <v>63</v>
-      </c>
-      <c r="L42" t="s">
-        <v>63</v>
-      </c>
-      <c r="M42" t="s">
-        <v>63</v>
-      </c>
-      <c r="N42" t="s">
-        <v>63</v>
+      <c r="C42">
+        <v>5</v>
+      </c>
+      <c r="D42">
+        <v>5</v>
+      </c>
+      <c r="E42">
+        <v>5</v>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42">
+        <v>5</v>
+      </c>
+      <c r="H42">
+        <v>5</v>
+      </c>
+      <c r="I42">
+        <v>5</v>
+      </c>
+      <c r="J42">
+        <v>5</v>
+      </c>
+      <c r="K42">
+        <v>5</v>
+      </c>
+      <c r="L42">
+        <v>5</v>
+      </c>
+      <c r="M42">
+        <v>5</v>
+      </c>
+      <c r="N42">
+        <v>5</v>
       </c>
       <c r="O42">
         <v>5</v>
@@ -2701,41 +2668,41 @@
       <c r="A43" t="s">
         <v>62</v>
       </c>
-      <c r="C43">
-        <v>0.7</v>
-      </c>
-      <c r="D43">
-        <v>0.7</v>
-      </c>
-      <c r="E43">
-        <v>0.7</v>
-      </c>
-      <c r="F43">
-        <v>0.7</v>
-      </c>
-      <c r="G43">
-        <v>0.7</v>
-      </c>
-      <c r="H43">
-        <v>0.7</v>
-      </c>
-      <c r="I43">
-        <v>0.7</v>
-      </c>
-      <c r="J43">
-        <v>0.7</v>
-      </c>
-      <c r="K43">
-        <v>0.7</v>
-      </c>
-      <c r="L43">
-        <v>0.7</v>
-      </c>
-      <c r="M43">
-        <v>0.7</v>
-      </c>
-      <c r="N43">
-        <v>0.7</v>
+      <c r="C43" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" t="s">
+        <v>78</v>
+      </c>
+      <c r="E43" t="s">
+        <v>78</v>
+      </c>
+      <c r="F43" t="s">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" t="s">
+        <v>78</v>
+      </c>
+      <c r="I43" t="s">
+        <v>63</v>
+      </c>
+      <c r="J43" t="s">
+        <v>63</v>
+      </c>
+      <c r="K43" t="s">
+        <v>63</v>
+      </c>
+      <c r="L43" t="s">
+        <v>63</v>
+      </c>
+      <c r="M43" t="s">
+        <v>63</v>
+      </c>
+      <c r="N43" t="s">
+        <v>63</v>
       </c>
       <c r="O43" t="s">
         <v>63</v>
@@ -2761,40 +2728,40 @@
         <v>64</v>
       </c>
       <c r="C44">
-        <v>40</v>
+        <v>0.7</v>
       </c>
       <c r="D44">
-        <v>40</v>
+        <v>0.7</v>
       </c>
       <c r="E44">
-        <v>40</v>
+        <v>0.7</v>
       </c>
       <c r="F44">
-        <v>40</v>
+        <v>0.7</v>
       </c>
       <c r="G44">
-        <v>40</v>
+        <v>0.7</v>
       </c>
       <c r="H44">
-        <v>40</v>
+        <v>0.7</v>
       </c>
       <c r="I44">
-        <v>40</v>
+        <v>0.7</v>
       </c>
       <c r="J44">
-        <v>40</v>
+        <v>0.7</v>
       </c>
       <c r="K44">
-        <v>40</v>
+        <v>0.7</v>
       </c>
       <c r="L44">
-        <v>40</v>
+        <v>0.7</v>
       </c>
       <c r="M44">
-        <v>40</v>
+        <v>0.7</v>
       </c>
       <c r="N44">
-        <v>40</v>
+        <v>0.7</v>
       </c>
       <c r="O44">
         <v>0.7</v>
@@ -2819,6 +2786,42 @@
       <c r="A45" t="s">
         <v>65</v>
       </c>
+      <c r="C45">
+        <v>40</v>
+      </c>
+      <c r="D45">
+        <v>40</v>
+      </c>
+      <c r="E45">
+        <v>40</v>
+      </c>
+      <c r="F45">
+        <v>40</v>
+      </c>
+      <c r="G45">
+        <v>40</v>
+      </c>
+      <c r="H45">
+        <v>40</v>
+      </c>
+      <c r="I45">
+        <v>40</v>
+      </c>
+      <c r="J45">
+        <v>40</v>
+      </c>
+      <c r="K45">
+        <v>40</v>
+      </c>
+      <c r="L45">
+        <v>40</v>
+      </c>
+      <c r="M45">
+        <v>40</v>
+      </c>
+      <c r="N45">
+        <v>40</v>
+      </c>
       <c r="O45">
         <v>40</v>
       </c>
@@ -2841,7 +2844,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="O1:T45 A1:B45" numberStoredAsText="1"/>
+    <ignoredError sqref="O1:T5 A1:B45 O7:T45" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/online_experiment/crowding_stationary_dynamic_flies_online.xlsx
+++ b/online_experiment/crowding_stationary_dynamic_flies_online.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/helenhu/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/helenhu/Documents/GitHub/crowded-dynamic-fixation/online_experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4748C680-3943-A14E-A697-574E56FD8E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF67B430-8A2A-3F4E-818E-B8BE71D98A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="760" windowWidth="29240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="900" yWindow="700" windowWidth="12480" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1617,7 +1617,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:20" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -3341,7 +3341,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A26:T28 A67:T67 A30:B30 A31:T32 A1:T2 A40:T65 A39:B39 F39:H39 Q39:T39 A34:T36 A33:B33 K39:N39 A38:T38 A37:B37" numberStoredAsText="1"/>
+    <ignoredError sqref="A26:T28 A67:T67 A30:B30 A31:T32 A1:T2 A40:T62 A39:B39 F39:H39 Q39:T39 A34:T36 A33:B33 K39:N39 A38:T38 A37:B37 A64:T65 A63:B63" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>